--- a/Acordos.xlsx
+++ b/Acordos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\061583881\Downloads\Atualização app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\urano\Setor_Area\Exportação\Institucional e Food Service\INTELIGÊNCIA COMERCIAL\Histórico e PVG 2025\ATUALIZAÇÃO APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319E702B-B2F1-4EB6-8FC1-6AC98C91F0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{146053AD-6B33-4DD0-AC31-419C7F51ADE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{26CED4ED-5781-4158-9309-97F3C42298B0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26CED4ED-5781-4158-9309-97F3C42298B0}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE ACORDOS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6899" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="722">
   <si>
     <t>Gerente</t>
   </si>
@@ -2284,6 +2284,9 @@
     <t>Investimento de Sell in em: Manteiga bloco 5kg</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
     <t>Investimento de Sell in em: Manteiga blister com e sem sal -  Itambé</t>
   </si>
   <si>
@@ -2293,11 +2296,51 @@
     <t>Erro Operacional</t>
   </si>
   <si>
+    <t>Rodrigo</t>
+  </si>
+  <si>
     <t>Verba</t>
   </si>
   <si>
-    <t xml:space="preserve">Investimento de Rebate 4% em: Doce de Leite R$ 3.428,12, Leite Condensado R$ 5.631,91, Creme de Leite R$ 1.958,92, Manteiga R$ 489,73, LPI R$ 734,60
+    <t>Investimento na Campanha Anual Oesa - Cota Bronze (Parcela 06/09) Valor Total Do Acordo R$20.000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimento de sell in referente à vendas de setembro 2026 itambé  SKU: DOCE DE LEITE  R$ 206,71 ; LEITE CONDENSADO  R$ 4.102,03 ; LEITE EM PÓ  R$ 1.158,48 ;CREME UHT  R$ 308,12.
 </t>
+  </si>
+  <si>
+    <t>Investimento de Sell In, SKU: 610405337 - MANTEIGA C/SAL BLISTER 10G PRESIDENT TEU; 610402337 - MANTEIGA S/SAL BLISTER 10G PRESIDENT TEU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimento em sell in referente às vendas de outubro 26 itambé, Categoria: Composto R$ 114,65, Creme R$ 36,72, Doce R$ 137,64, Leite Condensado R$ 507,90, ManteigaR$ 29,63 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimento de Sell In referente às vendas de setembro 26, Creme de Leite  R$ 1.110,47, Leite Condensado R$ 8.889,53 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimennto em sell in referente às vendas de setembro 2026, Categorias: Creme de Leite  R$ 856,81, Doce de Leite R$ 393,30, Leite Condensado R$ 931,00 </t>
+  </si>
+  <si>
+    <t>DIST DE ALIMENTOS DEQUECH LTDA</t>
+  </si>
+  <si>
+    <t>Parcela 1 de investimento na Campanha de Verão Dequech 2026 - essa campanha tem por objetivo incentivar a marca no distribuidor para garantir o crescimento das seguintes categorias: Leite Condensado e Composto culinário, além de cadastro de novos Skus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5016719	</t>
+  </si>
+  <si>
+    <t>PENNACCHI E CIA LTDA</t>
+  </si>
+  <si>
+    <t>1/3 Pagamento referente a pendencias de ações realizadas para sell out e FIFO no ano passado -pagamento para reativação de cliente e retomada de mercado , mediante a pedido mínimo de R$25.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimento em sell in venda outubro 2026, categoria: Creme  R$ 758,72 , Doce de Leite R$ 57,35, Leite Condensado R $296.34 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investimento em sell in venda outubro 2026, Categoria: Leite Condensado  R$ 1.785,82, Doce de Leite R$ 219,67 </t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2433,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2478,6 +2521,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2857,34 +2906,34 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:W468"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:W477"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="9.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="2"/>
-    <col min="4" max="4" width="11.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="2"/>
+    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="2"/>
+    <col min="4" max="4" width="11.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17" style="19" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.88671875" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="20" max="22" width="9" style="10" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="14.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2955,7 +3004,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>398</v>
       </c>
@@ -3026,7 +3075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>398</v>
       </c>
@@ -3097,7 +3146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>398</v>
       </c>
@@ -3168,7 +3217,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>398</v>
       </c>
@@ -3239,7 +3288,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>398</v>
       </c>
@@ -3310,7 +3359,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>398</v>
       </c>
@@ -3381,7 +3430,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>398</v>
       </c>
@@ -3452,7 +3501,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>398</v>
       </c>
@@ -3523,7 +3572,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>398</v>
       </c>
@@ -3594,7 +3643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>398</v>
       </c>
@@ -3665,7 +3714,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>398</v>
       </c>
@@ -3736,7 +3785,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>398</v>
       </c>
@@ -3807,7 +3856,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>398</v>
       </c>
@@ -3878,7 +3927,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>398</v>
       </c>
@@ -3949,7 +3998,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>398</v>
       </c>
@@ -4020,7 +4069,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>398</v>
       </c>
@@ -4091,7 +4140,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>398</v>
       </c>
@@ -4162,7 +4211,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>398</v>
       </c>
@@ -4233,7 +4282,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>398</v>
       </c>
@@ -4304,7 +4353,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>398</v>
       </c>
@@ -4375,7 +4424,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>398</v>
       </c>
@@ -4446,7 +4495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>398</v>
       </c>
@@ -4517,7 +4566,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>398</v>
       </c>
@@ -4588,7 +4637,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>398</v>
       </c>
@@ -4656,7 +4705,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>398</v>
       </c>
@@ -4727,7 +4776,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>398</v>
       </c>
@@ -4798,7 +4847,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>398</v>
       </c>
@@ -4869,7 +4918,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>398</v>
       </c>
@@ -4940,7 +4989,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>398</v>
       </c>
@@ -5011,7 +5060,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>398</v>
       </c>
@@ -5082,7 +5131,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>398</v>
       </c>
@@ -5153,7 +5202,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>398</v>
       </c>
@@ -5224,7 +5273,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>398</v>
       </c>
@@ -5295,7 +5344,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>398</v>
       </c>
@@ -5366,7 +5415,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>398</v>
       </c>
@@ -5437,7 +5486,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>398</v>
       </c>
@@ -5508,7 +5557,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>398</v>
       </c>
@@ -5579,7 +5628,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>398</v>
       </c>
@@ -5650,7 +5699,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>398</v>
       </c>
@@ -5721,7 +5770,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>398</v>
       </c>
@@ -5792,7 +5841,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>398</v>
       </c>
@@ -5863,7 +5912,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>398</v>
       </c>
@@ -5934,7 +5983,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>398</v>
       </c>
@@ -6005,7 +6054,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>398</v>
       </c>
@@ -6076,7 +6125,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>398</v>
       </c>
@@ -6147,7 +6196,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>398</v>
       </c>
@@ -6218,7 +6267,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>398</v>
       </c>
@@ -6289,7 +6338,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>398</v>
       </c>
@@ -6360,7 +6409,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>398</v>
       </c>
@@ -6431,7 +6480,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>398</v>
       </c>
@@ -6502,7 +6551,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>398</v>
       </c>
@@ -6573,7 +6622,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>398</v>
       </c>
@@ -6644,7 +6693,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>398</v>
       </c>
@@ -6715,7 +6764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>398</v>
       </c>
@@ -6786,7 +6835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>398</v>
       </c>
@@ -6857,7 +6906,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>398</v>
       </c>
@@ -6928,7 +6977,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>398</v>
       </c>
@@ -6996,7 +7045,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>398</v>
       </c>
@@ -7067,7 +7116,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>398</v>
       </c>
@@ -7138,7 +7187,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>398</v>
       </c>
@@ -7209,7 +7258,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>398</v>
       </c>
@@ -7280,7 +7329,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>398</v>
       </c>
@@ -7351,7 +7400,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>398</v>
       </c>
@@ -7422,7 +7471,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>398</v>
       </c>
@@ -7493,7 +7542,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>398</v>
       </c>
@@ -7564,7 +7613,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>398</v>
       </c>
@@ -7635,7 +7684,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>398</v>
       </c>
@@ -7706,7 +7755,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>398</v>
       </c>
@@ -7777,7 +7826,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>398</v>
       </c>
@@ -7848,7 +7897,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>398</v>
       </c>
@@ -7919,7 +7968,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>398</v>
       </c>
@@ -7990,7 +8039,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>398</v>
       </c>
@@ -8061,7 +8110,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>398</v>
       </c>
@@ -8132,7 +8181,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>398</v>
       </c>
@@ -8203,7 +8252,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>398</v>
       </c>
@@ -8274,7 +8323,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>398</v>
       </c>
@@ -8345,7 +8394,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>398</v>
       </c>
@@ -8416,7 +8465,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>398</v>
       </c>
@@ -8487,7 +8536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>398</v>
       </c>
@@ -8558,7 +8607,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>398</v>
       </c>
@@ -8629,7 +8678,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>398</v>
       </c>
@@ -8700,7 +8749,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>398</v>
       </c>
@@ -8771,7 +8820,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>398</v>
       </c>
@@ -8839,7 +8888,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>398</v>
       </c>
@@ -8910,7 +8959,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>398</v>
       </c>
@@ -8981,7 +9030,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>398</v>
       </c>
@@ -9052,7 +9101,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>398</v>
       </c>
@@ -9123,7 +9172,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>398</v>
       </c>
@@ -9194,7 +9243,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>398</v>
       </c>
@@ -9265,7 +9314,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>398</v>
       </c>
@@ -9336,7 +9385,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>398</v>
       </c>
@@ -9407,7 +9456,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>398</v>
       </c>
@@ -9478,7 +9527,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>398</v>
       </c>
@@ -9549,7 +9598,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>398</v>
       </c>
@@ -9620,7 +9669,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>398</v>
       </c>
@@ -9691,7 +9740,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>398</v>
       </c>
@@ -9762,7 +9811,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>398</v>
       </c>
@@ -9833,7 +9882,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>398</v>
       </c>
@@ -9904,7 +9953,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>398</v>
       </c>
@@ -9975,7 +10024,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>398</v>
       </c>
@@ -10046,7 +10095,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>398</v>
       </c>
@@ -10117,7 +10166,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>398</v>
       </c>
@@ -10188,7 +10237,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>398</v>
       </c>
@@ -10259,7 +10308,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>398</v>
       </c>
@@ -10330,7 +10379,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>436</v>
       </c>
@@ -10401,7 +10450,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>398</v>
       </c>
@@ -10472,7 +10521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>398</v>
       </c>
@@ -10543,7 +10592,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>398</v>
       </c>
@@ -10614,7 +10663,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>398</v>
       </c>
@@ -10685,7 +10734,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>398</v>
       </c>
@@ -10756,7 +10805,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>398</v>
       </c>
@@ -10827,7 +10876,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>398</v>
       </c>
@@ -10898,7 +10947,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>398</v>
       </c>
@@ -10966,7 +11015,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>398</v>
       </c>
@@ -11037,7 +11086,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>398</v>
       </c>
@@ -11108,7 +11157,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>398</v>
       </c>
@@ -11179,7 +11228,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>398</v>
       </c>
@@ -11250,7 +11299,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>398</v>
       </c>
@@ -11321,7 +11370,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>398</v>
       </c>
@@ -11392,7 +11441,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>398</v>
       </c>
@@ -11463,7 +11512,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>398</v>
       </c>
@@ -11534,7 +11583,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>398</v>
       </c>
@@ -11605,7 +11654,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>398</v>
       </c>
@@ -11676,7 +11725,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>398</v>
       </c>
@@ -11747,7 +11796,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>398</v>
       </c>
@@ -11818,7 +11867,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>398</v>
       </c>
@@ -11886,7 +11935,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>398</v>
       </c>
@@ -11957,7 +12006,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>398</v>
       </c>
@@ -12028,7 +12077,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>398</v>
       </c>
@@ -12099,7 +12148,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>398</v>
       </c>
@@ -12170,7 +12219,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>398</v>
       </c>
@@ -12241,7 +12290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>398</v>
       </c>
@@ -12309,7 +12358,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>398</v>
       </c>
@@ -12380,7 +12429,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>398</v>
       </c>
@@ -12451,7 +12500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>398</v>
       </c>
@@ -12522,7 +12571,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>398</v>
       </c>
@@ -12593,7 +12642,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>398</v>
       </c>
@@ -12664,7 +12713,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>398</v>
       </c>
@@ -12735,7 +12784,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>398</v>
       </c>
@@ -12806,7 +12855,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>398</v>
       </c>
@@ -12877,7 +12926,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>398</v>
       </c>
@@ -12948,7 +12997,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>398</v>
       </c>
@@ -13019,7 +13068,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>398</v>
       </c>
@@ -13090,7 +13139,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>398</v>
       </c>
@@ -13161,7 +13210,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>398</v>
       </c>
@@ -13232,7 +13281,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>398</v>
       </c>
@@ -13303,7 +13352,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>398</v>
       </c>
@@ -13374,7 +13423,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>398</v>
       </c>
@@ -13445,7 +13494,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>398</v>
       </c>
@@ -13516,7 +13565,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>398</v>
       </c>
@@ -13587,7 +13636,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>398</v>
       </c>
@@ -13658,7 +13707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>398</v>
       </c>
@@ -13729,7 +13778,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>398</v>
       </c>
@@ -13800,7 +13849,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>398</v>
       </c>
@@ -13871,7 +13920,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>398</v>
       </c>
@@ -13942,7 +13991,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>398</v>
       </c>
@@ -14013,7 +14062,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>398</v>
       </c>
@@ -14084,7 +14133,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>398</v>
       </c>
@@ -14155,7 +14204,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>398</v>
       </c>
@@ -14226,7 +14275,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>398</v>
       </c>
@@ -14297,7 +14346,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>398</v>
       </c>
@@ -14368,7 +14417,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>398</v>
       </c>
@@ -14439,7 +14488,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>398</v>
       </c>
@@ -14510,7 +14559,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>398</v>
       </c>
@@ -14581,7 +14630,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>398</v>
       </c>
@@ -14652,7 +14701,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>398</v>
       </c>
@@ -14723,7 +14772,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>398</v>
       </c>
@@ -14794,7 +14843,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>398</v>
       </c>
@@ -14865,7 +14914,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>398</v>
       </c>
@@ -14936,7 +14985,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>398</v>
       </c>
@@ -15007,7 +15056,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>398</v>
       </c>
@@ -15078,7 +15127,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>398</v>
       </c>
@@ -15149,7 +15198,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>398</v>
       </c>
@@ -15220,7 +15269,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>398</v>
       </c>
@@ -15291,7 +15340,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>398</v>
       </c>
@@ -15362,7 +15411,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>398</v>
       </c>
@@ -15433,7 +15482,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>398</v>
       </c>
@@ -15504,7 +15553,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>398</v>
       </c>
@@ -15575,7 +15624,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>398</v>
       </c>
@@ -15646,7 +15695,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>398</v>
       </c>
@@ -15717,7 +15766,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>398</v>
       </c>
@@ -15788,7 +15837,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>398</v>
       </c>
@@ -15859,7 +15908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>398</v>
       </c>
@@ -15930,7 +15979,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>398</v>
       </c>
@@ -16001,7 +16050,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>398</v>
       </c>
@@ -16072,7 +16121,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>398</v>
       </c>
@@ -16143,7 +16192,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>398</v>
       </c>
@@ -16214,7 +16263,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>398</v>
       </c>
@@ -16285,7 +16334,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>398</v>
       </c>
@@ -16356,7 +16405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>398</v>
       </c>
@@ -16427,7 +16476,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>398</v>
       </c>
@@ -16498,7 +16547,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>398</v>
       </c>
@@ -16569,7 +16618,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>398</v>
       </c>
@@ -16640,7 +16689,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>398</v>
       </c>
@@ -16711,7 +16760,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>398</v>
       </c>
@@ -16782,7 +16831,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>398</v>
       </c>
@@ -16853,7 +16902,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>398</v>
       </c>
@@ -16924,7 +16973,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>398</v>
       </c>
@@ -16995,7 +17044,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>398</v>
       </c>
@@ -17066,7 +17115,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>398</v>
       </c>
@@ -17137,7 +17186,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>398</v>
       </c>
@@ -17208,7 +17257,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>398</v>
       </c>
@@ -17279,7 +17328,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>398</v>
       </c>
@@ -17350,7 +17399,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>398</v>
       </c>
@@ -17421,7 +17470,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="206" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>398</v>
       </c>
@@ -17492,7 +17541,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>398</v>
       </c>
@@ -17563,7 +17612,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>398</v>
       </c>
@@ -17634,7 +17683,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="209" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>398</v>
       </c>
@@ -17705,7 +17754,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>398</v>
       </c>
@@ -17776,7 +17825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>398</v>
       </c>
@@ -17847,7 +17896,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>398</v>
       </c>
@@ -17915,7 +17964,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>398</v>
       </c>
@@ -17986,7 +18035,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>398</v>
       </c>
@@ -18057,7 +18106,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>398</v>
       </c>
@@ -18128,7 +18177,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>398</v>
       </c>
@@ -18199,7 +18248,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>398</v>
       </c>
@@ -18270,7 +18319,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="218" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>398</v>
       </c>
@@ -18338,7 +18387,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="219" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>398</v>
       </c>
@@ -18409,7 +18458,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>398</v>
       </c>
@@ -18480,7 +18529,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="221" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>398</v>
       </c>
@@ -18548,7 +18597,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>398</v>
       </c>
@@ -18619,7 +18668,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="223" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>398</v>
       </c>
@@ -18690,7 +18739,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="224" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>398</v>
       </c>
@@ -18761,7 +18810,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>398</v>
       </c>
@@ -18832,7 +18881,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>398</v>
       </c>
@@ -18903,7 +18952,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>398</v>
       </c>
@@ -18974,7 +19023,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>398</v>
       </c>
@@ -19045,7 +19094,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>398</v>
       </c>
@@ -19116,7 +19165,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>398</v>
       </c>
@@ -19187,7 +19236,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>398</v>
       </c>
@@ -19258,7 +19307,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>398</v>
       </c>
@@ -19329,7 +19378,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>398</v>
       </c>
@@ -19400,7 +19449,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>398</v>
       </c>
@@ -19471,7 +19520,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>398</v>
       </c>
@@ -19542,7 +19591,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>398</v>
       </c>
@@ -19613,7 +19662,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>398</v>
       </c>
@@ -19684,7 +19733,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>398</v>
       </c>
@@ -19755,7 +19804,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>398</v>
       </c>
@@ -19826,7 +19875,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>398</v>
       </c>
@@ -19897,7 +19946,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>398</v>
       </c>
@@ -19965,7 +20014,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>398</v>
       </c>
@@ -20036,7 +20085,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>398</v>
       </c>
@@ -20107,7 +20156,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>398</v>
       </c>
@@ -20178,7 +20227,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>436</v>
       </c>
@@ -20246,7 +20295,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>436</v>
       </c>
@@ -20314,7 +20363,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>398</v>
       </c>
@@ -20385,7 +20434,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>398</v>
       </c>
@@ -20456,7 +20505,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>398</v>
       </c>
@@ -20527,7 +20576,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>398</v>
       </c>
@@ -20598,7 +20647,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>398</v>
       </c>
@@ -20669,7 +20718,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>398</v>
       </c>
@@ -20740,7 +20789,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>398</v>
       </c>
@@ -20811,7 +20860,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>398</v>
       </c>
@@ -20882,7 +20931,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>398</v>
       </c>
@@ -20953,7 +21002,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>398</v>
       </c>
@@ -21024,7 +21073,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>398</v>
       </c>
@@ -21095,7 +21144,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>398</v>
       </c>
@@ -21166,7 +21215,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>398</v>
       </c>
@@ -21237,7 +21286,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>398</v>
       </c>
@@ -21308,7 +21357,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>398</v>
       </c>
@@ -21379,7 +21428,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>398</v>
       </c>
@@ -21450,7 +21499,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>398</v>
       </c>
@@ -21521,7 +21570,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>398</v>
       </c>
@@ -21592,7 +21641,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>398</v>
       </c>
@@ -21663,7 +21712,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>398</v>
       </c>
@@ -21734,7 +21783,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>398</v>
       </c>
@@ -21805,7 +21854,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>398</v>
       </c>
@@ -21876,7 +21925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>398</v>
       </c>
@@ -21947,7 +21996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>398</v>
       </c>
@@ -22018,7 +22067,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>398</v>
       </c>
@@ -22089,7 +22138,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>398</v>
       </c>
@@ -22160,7 +22209,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>398</v>
       </c>
@@ -22231,7 +22280,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>398</v>
       </c>
@@ -22302,7 +22351,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>398</v>
       </c>
@@ -22373,7 +22422,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>398</v>
       </c>
@@ -22444,7 +22493,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>398</v>
       </c>
@@ -22515,7 +22564,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>398</v>
       </c>
@@ -22586,7 +22635,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>398</v>
       </c>
@@ -22657,7 +22706,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>398</v>
       </c>
@@ -22728,7 +22777,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>398</v>
       </c>
@@ -22799,7 +22848,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>398</v>
       </c>
@@ -22870,7 +22919,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>398</v>
       </c>
@@ -22941,7 +22990,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="284" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>398</v>
       </c>
@@ -23012,7 +23061,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="285" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>398</v>
       </c>
@@ -23083,7 +23132,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="286" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>398</v>
       </c>
@@ -23154,7 +23203,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>398</v>
       </c>
@@ -23225,7 +23274,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>398</v>
       </c>
@@ -23296,7 +23345,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>398</v>
       </c>
@@ -23367,7 +23416,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>398</v>
       </c>
@@ -23438,7 +23487,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>398</v>
       </c>
@@ -23509,7 +23558,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>398</v>
       </c>
@@ -23580,7 +23629,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="293" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>398</v>
       </c>
@@ -23651,7 +23700,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="294" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>398</v>
       </c>
@@ -23722,7 +23771,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>398</v>
       </c>
@@ -23793,7 +23842,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>398</v>
       </c>
@@ -23864,7 +23913,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>398</v>
       </c>
@@ -23935,7 +23984,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="298" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>398</v>
       </c>
@@ -24006,7 +24055,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>398</v>
       </c>
@@ -24077,7 +24126,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>398</v>
       </c>
@@ -24148,7 +24197,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="301" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>398</v>
       </c>
@@ -24219,7 +24268,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>398</v>
       </c>
@@ -24290,7 +24339,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>398</v>
       </c>
@@ -24361,7 +24410,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>398</v>
       </c>
@@ -24432,7 +24481,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>398</v>
       </c>
@@ -24503,7 +24552,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>398</v>
       </c>
@@ -24574,7 +24623,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>398</v>
       </c>
@@ -24645,7 +24694,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>436</v>
       </c>
@@ -24716,7 +24765,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>398</v>
       </c>
@@ -24787,7 +24836,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>398</v>
       </c>
@@ -24858,7 +24907,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>398</v>
       </c>
@@ -24929,7 +24978,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>398</v>
       </c>
@@ -25000,7 +25049,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="313" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>398</v>
       </c>
@@ -25071,7 +25120,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>398</v>
       </c>
@@ -25142,7 +25191,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>398</v>
       </c>
@@ -25213,7 +25262,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>398</v>
       </c>
@@ -25284,7 +25333,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>398</v>
       </c>
@@ -25355,7 +25404,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>398</v>
       </c>
@@ -25426,7 +25475,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>398</v>
       </c>
@@ -25497,7 +25546,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>398</v>
       </c>
@@ -25568,7 +25617,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="321" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>398</v>
       </c>
@@ -25639,7 +25688,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="322" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>398</v>
       </c>
@@ -25710,7 +25759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="323" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>398</v>
       </c>
@@ -25781,7 +25830,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="324" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>398</v>
       </c>
@@ -25852,7 +25901,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="325" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>398</v>
       </c>
@@ -25923,7 +25972,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="326" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>398</v>
       </c>
@@ -25994,7 +26043,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="327" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>398</v>
       </c>
@@ -26065,7 +26114,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="328" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>398</v>
       </c>
@@ -26136,7 +26185,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="329" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>398</v>
       </c>
@@ -26207,7 +26256,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="330" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>398</v>
       </c>
@@ -26278,7 +26327,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="331" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>398</v>
       </c>
@@ -26349,7 +26398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="332" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>398</v>
       </c>
@@ -26420,7 +26469,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="333" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>398</v>
       </c>
@@ -26491,7 +26540,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="334" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>398</v>
       </c>
@@ -26562,7 +26611,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="335" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>398</v>
       </c>
@@ -26633,7 +26682,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>398</v>
       </c>
@@ -26704,7 +26753,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>398</v>
       </c>
@@ -26775,7 +26824,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="338" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>398</v>
       </c>
@@ -26846,7 +26895,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="339" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>398</v>
       </c>
@@ -26914,7 +26963,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="340" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>398</v>
       </c>
@@ -26982,7 +27031,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="341" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>398</v>
       </c>
@@ -27053,7 +27102,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="342" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>398</v>
       </c>
@@ -27124,7 +27173,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="343" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>398</v>
       </c>
@@ -27195,7 +27244,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="344" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>398</v>
       </c>
@@ -27266,7 +27315,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="345" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>398</v>
       </c>
@@ -27337,7 +27386,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="346" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>398</v>
       </c>
@@ -27408,7 +27457,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="347" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>398</v>
       </c>
@@ -27479,7 +27528,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="348" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>398</v>
       </c>
@@ -27550,7 +27599,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="349" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>398</v>
       </c>
@@ -27621,7 +27670,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="350" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>398</v>
       </c>
@@ -27692,7 +27741,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="351" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>398</v>
       </c>
@@ -27763,7 +27812,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="352" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>398</v>
       </c>
@@ -27834,7 +27883,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>398</v>
       </c>
@@ -27905,7 +27954,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>398</v>
       </c>
@@ -27976,7 +28025,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>398</v>
       </c>
@@ -28047,7 +28096,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>398</v>
       </c>
@@ -28118,7 +28167,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>398</v>
       </c>
@@ -28189,7 +28238,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>398</v>
       </c>
@@ -28260,7 +28309,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>398</v>
       </c>
@@ -28331,7 +28380,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="360" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>398</v>
       </c>
@@ -28402,7 +28451,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="361" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>398</v>
       </c>
@@ -28473,7 +28522,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="362" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>398</v>
       </c>
@@ -28544,7 +28593,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>398</v>
       </c>
@@ -28615,7 +28664,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>398</v>
       </c>
@@ -28686,7 +28735,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="365" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>398</v>
       </c>
@@ -28757,7 +28806,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>398</v>
       </c>
@@ -28828,7 +28877,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="367" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>398</v>
       </c>
@@ -28899,7 +28948,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="368" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>398</v>
       </c>
@@ -28970,7 +29019,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="369" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>398</v>
       </c>
@@ -29041,7 +29090,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="370" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>398</v>
       </c>
@@ -29112,7 +29161,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>398</v>
       </c>
@@ -29183,7 +29232,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="372" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>398</v>
       </c>
@@ -29254,7 +29303,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>398</v>
       </c>
@@ -29325,7 +29374,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="374" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>398</v>
       </c>
@@ -29396,7 +29445,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>398</v>
       </c>
@@ -29467,7 +29516,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="376" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>398</v>
       </c>
@@ -29538,7 +29587,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="377" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>398</v>
       </c>
@@ -29609,7 +29658,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="378" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>398</v>
       </c>
@@ -29680,7 +29729,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="379" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>398</v>
       </c>
@@ -29751,7 +29800,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="380" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>398</v>
       </c>
@@ -29822,7 +29871,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>398</v>
       </c>
@@ -29893,7 +29942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="382" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>398</v>
       </c>
@@ -29964,7 +30013,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>398</v>
       </c>
@@ -30035,7 +30084,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="384" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>398</v>
       </c>
@@ -30106,7 +30155,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="385" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>398</v>
       </c>
@@ -30177,7 +30226,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>398</v>
       </c>
@@ -30248,7 +30297,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="387" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>398</v>
       </c>
@@ -30319,7 +30368,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="388" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>398</v>
       </c>
@@ -30390,7 +30439,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>398</v>
       </c>
@@ -30461,7 +30510,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="390" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>398</v>
       </c>
@@ -30532,7 +30581,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="391" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>398</v>
       </c>
@@ -30603,7 +30652,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="392" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>398</v>
       </c>
@@ -30674,7 +30723,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>398</v>
       </c>
@@ -30745,7 +30794,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="394" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>398</v>
       </c>
@@ -30816,7 +30865,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="395" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>398</v>
       </c>
@@ -30887,7 +30936,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="396" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>398</v>
       </c>
@@ -30958,7 +31007,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="397" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>398</v>
       </c>
@@ -31029,7 +31078,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="398" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>398</v>
       </c>
@@ -31100,7 +31149,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="399" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>398</v>
       </c>
@@ -31171,7 +31220,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="400" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>398</v>
       </c>
@@ -31242,7 +31291,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="401" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>398</v>
       </c>
@@ -31313,7 +31362,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="402" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>398</v>
       </c>
@@ -31384,7 +31433,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="403" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>398</v>
       </c>
@@ -31455,7 +31504,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="404" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>398</v>
       </c>
@@ -31526,7 +31575,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="405" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>398</v>
       </c>
@@ -31597,7 +31646,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="406" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>398</v>
       </c>
@@ -31668,7 +31717,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="407" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>398</v>
       </c>
@@ -31739,7 +31788,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="408" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>398</v>
       </c>
@@ -31810,7 +31859,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="409" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>398</v>
       </c>
@@ -31881,7 +31930,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="410" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>398</v>
       </c>
@@ -31952,7 +32001,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="411" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>398</v>
       </c>
@@ -32023,7 +32072,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="412" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>398</v>
       </c>
@@ -32094,7 +32143,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="413" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>398</v>
       </c>
@@ -32162,7 +32211,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="414" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>398</v>
       </c>
@@ -32233,7 +32282,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="415" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>398</v>
       </c>
@@ -32304,7 +32353,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="416" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>398</v>
       </c>
@@ -32375,7 +32424,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="417" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>398</v>
       </c>
@@ -32446,7 +32495,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="418" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>398</v>
       </c>
@@ -32517,7 +32566,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="419" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>398</v>
       </c>
@@ -32588,7 +32637,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="420" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>398</v>
       </c>
@@ -32659,7 +32708,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="421" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>398</v>
       </c>
@@ -32730,7 +32779,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="422" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>398</v>
       </c>
@@ -32801,7 +32850,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="423" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>398</v>
       </c>
@@ -32872,7 +32921,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="424" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>398</v>
       </c>
@@ -32943,7 +32992,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="425" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>398</v>
       </c>
@@ -33014,7 +33063,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="426" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>398</v>
       </c>
@@ -33085,7 +33134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="427" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>398</v>
       </c>
@@ -33156,7 +33205,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="428" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>398</v>
       </c>
@@ -33227,7 +33276,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="429" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>398</v>
       </c>
@@ -33298,7 +33347,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="430" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>398</v>
       </c>
@@ -33369,7 +33418,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="431" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>398</v>
       </c>
@@ -33440,7 +33489,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="432" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>398</v>
       </c>
@@ -33511,7 +33560,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="433" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>398</v>
       </c>
@@ -33582,7 +33631,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="434" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>398</v>
       </c>
@@ -33653,7 +33702,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="435" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>398</v>
       </c>
@@ -33724,7 +33773,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="436" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>436</v>
       </c>
@@ -33795,7 +33844,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="437" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>398</v>
       </c>
@@ -33864,7 +33913,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="438" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>398</v>
       </c>
@@ -33935,7 +33984,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="439" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>398</v>
       </c>
@@ -34003,7 +34052,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="440" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>398</v>
       </c>
@@ -34071,7 +34120,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="441" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>398</v>
       </c>
@@ -34142,7 +34191,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="442" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>398</v>
       </c>
@@ -34213,7 +34262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="443" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>398</v>
       </c>
@@ -34284,7 +34333,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="444" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>398</v>
       </c>
@@ -34355,7 +34404,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="445" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>398</v>
       </c>
@@ -34426,7 +34475,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="446" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>398</v>
       </c>
@@ -34497,7 +34546,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="447" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>398</v>
       </c>
@@ -34568,7 +34617,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="448" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>398</v>
       </c>
@@ -34639,7 +34688,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="449" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>398</v>
       </c>
@@ -34710,7 +34759,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="450" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>398</v>
       </c>
@@ -34781,7 +34830,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="451" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>398</v>
       </c>
@@ -34852,7 +34901,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="452" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>398</v>
       </c>
@@ -34923,7 +34972,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="453" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>398</v>
       </c>
@@ -34994,7 +35043,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="454" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>398</v>
       </c>
@@ -35065,7 +35114,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="455" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>398</v>
       </c>
@@ -35136,7 +35185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="456" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>398</v>
       </c>
@@ -35207,7 +35256,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="457" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>398</v>
       </c>
@@ -35278,7 +35327,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="458" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>398</v>
       </c>
@@ -35349,7 +35398,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="459" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>398</v>
       </c>
@@ -35420,7 +35469,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="460" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>398</v>
       </c>
@@ -35491,7 +35540,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="461" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>398</v>
       </c>
@@ -35562,7 +35611,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="462" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>398</v>
       </c>
@@ -35633,7 +35682,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="463" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>398</v>
       </c>
@@ -35704,7 +35753,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="464" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>398</v>
       </c>
@@ -35742,7 +35791,7 @@
         <v>702</v>
       </c>
       <c r="N464" s="6" t="s">
-        <v>25</v>
+        <v>703</v>
       </c>
       <c r="O464" s="21">
         <v>46302</v>
@@ -35772,7 +35821,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="465" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>398</v>
       </c>
@@ -35810,7 +35859,7 @@
         <v>702</v>
       </c>
       <c r="N465" s="6" t="s">
-        <v>25</v>
+        <v>703</v>
       </c>
       <c r="O465" s="21">
         <v>46302</v>
@@ -35840,7 +35889,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="466" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>398</v>
       </c>
@@ -35875,7 +35924,7 @@
         <v>93</v>
       </c>
       <c r="M466" s="19" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N466" s="7" t="s">
         <v>467</v>
@@ -35908,7 +35957,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="467" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>398</v>
       </c>
@@ -35946,7 +35995,7 @@
         <v>93</v>
       </c>
       <c r="M467" s="19" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N467" s="7" t="s">
         <v>467</v>
@@ -35976,30 +36025,33 @@
         <v>29</v>
       </c>
       <c r="W467" s="10" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="468" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A468" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B468" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="468" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A468" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B468" s="10" t="s">
         <v>697</v>
       </c>
       <c r="C468" s="2">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
+      </c>
+      <c r="E468" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="F468" s="3">
-        <v>5004685</v>
+        <v>5217293</v>
       </c>
       <c r="G468" s="3">
-        <v>110434</v>
+        <v>145966</v>
       </c>
       <c r="H468" s="3" t="s">
-        <v>116</v>
+        <v>507</v>
       </c>
       <c r="I468" s="3" t="s">
         <v>23</v>
@@ -36011,10 +36063,10 @@
         <v>192</v>
       </c>
       <c r="L468" s="5">
-        <v>93</v>
-      </c>
-      <c r="M468" s="19" t="s">
-        <v>707</v>
+        <v>92</v>
+      </c>
+      <c r="M468" s="30" t="s">
+        <v>709</v>
       </c>
       <c r="N468" s="7" t="s">
         <v>467</v>
@@ -36026,13 +36078,13 @@
         <v>398</v>
       </c>
       <c r="Q468" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R468" s="8" t="s">
-        <v>402</v>
+        <v>26</v>
+      </c>
+      <c r="R468" s="31" t="s">
+        <v>610</v>
       </c>
       <c r="S468" s="9">
-        <v>12243.28</v>
+        <v>2222.2199999999998</v>
       </c>
       <c r="T468" s="10" t="s">
         <v>27</v>
@@ -36044,7 +36096,646 @@
         <v>29</v>
       </c>
       <c r="W468" s="10" t="s">
-        <v>338</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="469" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A469" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B469" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C469" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E469" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F469" s="3">
+        <v>5006978</v>
+      </c>
+      <c r="G469" s="3">
+        <v>103036</v>
+      </c>
+      <c r="H469" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I469" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J469" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K469" s="3">
+        <v>722</v>
+      </c>
+      <c r="L469" s="5">
+        <v>92</v>
+      </c>
+      <c r="M469" s="30" t="s">
+        <v>710</v>
+      </c>
+      <c r="N469" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O469" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P469" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q469" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R469" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="S469" s="9">
+        <v>5775.34</v>
+      </c>
+      <c r="T469" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U469" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V469" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W469" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="470" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A470" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B470" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C470" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E470" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F470" s="3">
+        <v>5173494</v>
+      </c>
+      <c r="G470" s="3">
+        <v>185079</v>
+      </c>
+      <c r="H470" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="I470" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J470" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="K470" s="3">
+        <v>755</v>
+      </c>
+      <c r="L470" s="5">
+        <v>93</v>
+      </c>
+      <c r="M470" s="30" t="s">
+        <v>711</v>
+      </c>
+      <c r="N470" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O470" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P470" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q470" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="R470" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="S470" s="9">
+        <v>402</v>
+      </c>
+      <c r="T470" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U470" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="V470" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W470" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="471" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A471" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B471" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C471" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E471" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F471" s="3">
+        <v>5131101</v>
+      </c>
+      <c r="G471" s="3">
+        <v>167218</v>
+      </c>
+      <c r="H471" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I471" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J471" s="3">
+        <v>6125</v>
+      </c>
+      <c r="K471" s="3">
+        <v>692</v>
+      </c>
+      <c r="L471" s="5">
+        <v>93</v>
+      </c>
+      <c r="M471" s="30" t="s">
+        <v>712</v>
+      </c>
+      <c r="N471" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O471" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P471" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q471" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R471" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="S471" s="9">
+        <v>826.54</v>
+      </c>
+      <c r="T471" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U471" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V471" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W471" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="472" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A472" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B472" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C472" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D472" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E472" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F472" s="3">
+        <v>5109682</v>
+      </c>
+      <c r="G472" s="3">
+        <v>128100</v>
+      </c>
+      <c r="H472" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I472" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J472" s="3">
+        <v>6125</v>
+      </c>
+      <c r="K472" s="3">
+        <v>692</v>
+      </c>
+      <c r="L472" s="5">
+        <v>93</v>
+      </c>
+      <c r="M472" s="30" t="s">
+        <v>713</v>
+      </c>
+      <c r="N472" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O472" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P472" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q472" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R472" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="S472" s="9">
+        <v>10000</v>
+      </c>
+      <c r="T472" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U472" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V472" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W472" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="473" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A473" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B473" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C473" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D473" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E473" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F473" s="3">
+        <v>5023831</v>
+      </c>
+      <c r="G473" s="3">
+        <v>126676</v>
+      </c>
+      <c r="H473" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I473" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J473" s="3">
+        <v>6125</v>
+      </c>
+      <c r="K473" s="3">
+        <v>692</v>
+      </c>
+      <c r="L473" s="5">
+        <v>93</v>
+      </c>
+      <c r="M473" s="30" t="s">
+        <v>714</v>
+      </c>
+      <c r="N473" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O473" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P473" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q473" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R473" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="S473" s="9">
+        <v>2040</v>
+      </c>
+      <c r="T473" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U473" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V473" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W473" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="474" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B474" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C474" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D474" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E474" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F474" s="3">
+        <v>5015279</v>
+      </c>
+      <c r="G474" s="3">
+        <v>180836</v>
+      </c>
+      <c r="H474" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="I474" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="J474" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K474" s="3">
+        <v>193</v>
+      </c>
+      <c r="L474" s="5">
+        <v>93</v>
+      </c>
+      <c r="M474" s="30" t="s">
+        <v>716</v>
+      </c>
+      <c r="N474" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O474" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P474" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q474" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="R474" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="S474" s="9">
+        <v>500</v>
+      </c>
+      <c r="T474" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U474" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V474" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W474" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="475" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B475" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C475" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D475" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E475" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F475" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G475" s="3">
+        <v>108630</v>
+      </c>
+      <c r="H475" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="I475" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J475" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K475" s="3">
+        <v>195</v>
+      </c>
+      <c r="L475" s="5">
+        <v>92</v>
+      </c>
+      <c r="M475" s="30" t="s">
+        <v>719</v>
+      </c>
+      <c r="N475" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O475" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P475" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q475" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="R475" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="S475" s="9">
+        <v>11000</v>
+      </c>
+      <c r="T475" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U475" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V475" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W475" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="476" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B476" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C476" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D476" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E476" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F476" s="3">
+        <v>5023831</v>
+      </c>
+      <c r="G476" s="3">
+        <v>126676</v>
+      </c>
+      <c r="H476" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I476" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J476" s="3">
+        <v>6125</v>
+      </c>
+      <c r="K476" s="3">
+        <v>692</v>
+      </c>
+      <c r="L476" s="5">
+        <v>93</v>
+      </c>
+      <c r="M476" s="30" t="s">
+        <v>720</v>
+      </c>
+      <c r="N476" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O476" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P476" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q476" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R476" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="S476" s="9">
+        <v>1112.4100000000001</v>
+      </c>
+      <c r="T476" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U476" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V476" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W476" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="477" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B477" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C477" s="2">
+        <v>46310</v>
+      </c>
+      <c r="D477" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E477" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F477" s="3">
+        <v>5118346</v>
+      </c>
+      <c r="G477" s="3">
+        <v>143232</v>
+      </c>
+      <c r="H477" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I477" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J477" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="K477" s="3">
+        <v>192</v>
+      </c>
+      <c r="L477" s="5">
+        <v>93</v>
+      </c>
+      <c r="M477" s="30" t="s">
+        <v>721</v>
+      </c>
+      <c r="N477" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O477" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P477" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q477" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R477" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="S477" s="9">
+        <v>2005.49</v>
+      </c>
+      <c r="T477" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U477" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V477" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W477" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Acordos.xlsx
+++ b/Acordos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\urano\Setor_Area\Exportação\Institucional e Food Service\INTELIGÊNCIA COMERCIAL\Histórico e PVG 2025\ATUALIZAÇÃO APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{146053AD-6B33-4DD0-AC31-419C7F51ADE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{E763E810-6852-42F6-983F-8A87460C5E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26CED4ED-5781-4158-9309-97F3C42298B0}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE ACORDOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE ACORDOS'!$A$1:$W$462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE ACORDOS'!$A$1:$W$477</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7050" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7065" uniqueCount="723">
   <si>
     <t>Gerente</t>
   </si>
@@ -2341,6 +2341,9 @@
   </si>
   <si>
     <t xml:space="preserve">Investimento em sell in venda outubro 2026, Categoria: Leite Condensado  R$ 1.785,82, Doce de Leite R$ 219,67 </t>
+  </si>
+  <si>
+    <t>Investimento de Rebate 4% totalizando R$ 14.135,49; Doce de Leite R$ 3.957,94, Leite Condensado R$ 6.502,33, Creme de Leite R$ 2.261,68, Manteiga R$ 565,42, LPI R$ 848,13</t>
   </si>
 </sst>
 </file>
@@ -2433,7 +2436,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2527,6 +2530,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2906,7 +2912,7 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:W477"/>
+  <dimension ref="A1:W478"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="2"/>
@@ -35651,11 +35657,11 @@
       <c r="M462" s="19" t="s">
         <v>694</v>
       </c>
-      <c r="N462" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="O462" s="7" t="s">
-        <v>467</v>
+      <c r="N462" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O462" s="7">
+        <v>46296</v>
       </c>
       <c r="P462" s="3" t="s">
         <v>398</v>
@@ -35722,11 +35728,11 @@
       <c r="M463" s="19" t="s">
         <v>700</v>
       </c>
-      <c r="N463" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="O463" s="7" t="s">
-        <v>467</v>
+      <c r="N463" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O463" s="7">
+        <v>46296</v>
       </c>
       <c r="P463" s="3" t="s">
         <v>398</v>
@@ -36738,8 +36744,79 @@
         <v>60</v>
       </c>
     </row>
+    <row r="478" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B478" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C478" s="2">
+        <v>46314</v>
+      </c>
+      <c r="D478" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E478" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F478" s="3">
+        <v>5004685</v>
+      </c>
+      <c r="G478" s="3">
+        <v>110434</v>
+      </c>
+      <c r="H478" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I478" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J478" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="K478" s="3">
+        <v>192</v>
+      </c>
+      <c r="L478" s="5">
+        <v>92</v>
+      </c>
+      <c r="M478" s="32" t="s">
+        <v>722</v>
+      </c>
+      <c r="N478" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="O478" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="P478" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q478" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R478" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="S478" s="9">
+        <v>14135.49</v>
+      </c>
+      <c r="T478" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="U478" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V478" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W478" s="10" t="s">
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W462" xr:uid="{98AA0BDE-E6C8-4B65-9542-F70F3610FBA9}"/>
+  <autoFilter ref="A1:W477" xr:uid="{98AA0BDE-E6C8-4B65-9542-F70F3610FBA9}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>